--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R241"/>
+  <dimension ref="A1:T241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -593,6 +603,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -679,6 +699,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -765,6 +795,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -851,6 +891,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -937,6 +987,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1023,6 +1083,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1107,6 +1177,16 @@
           <t>030201</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1191,6 +1271,16 @@
           <t>030201</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1277,6 +1367,16 @@
           <t>030201</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1363,6 +1463,16 @@
           <t>030213</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1449,6 +1559,16 @@
           <t>030213</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1535,6 +1655,16 @@
           <t>030213</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1619,6 +1749,16 @@
           <t>030216</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1705,6 +1845,16 @@
           <t>030216</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1791,6 +1941,16 @@
           <t>040102</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1877,6 +2037,16 @@
           <t>040102</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1963,6 +2133,16 @@
           <t>040102</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2049,6 +2229,16 @@
           <t>040201</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2135,6 +2325,16 @@
           <t>040201</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2221,6 +2421,16 @@
           <t>040201</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2307,6 +2517,16 @@
           <t>040103</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2393,6 +2613,16 @@
           <t>040103</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2479,6 +2709,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2565,6 +2805,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2651,6 +2901,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2737,6 +2997,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2823,6 +3093,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2909,6 +3189,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2993,6 +3283,16 @@
           <t>040107</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3079,6 +3379,16 @@
           <t>040107</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3165,6 +3475,16 @@
           <t>040107</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3251,6 +3571,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3337,6 +3667,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3423,6 +3763,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3509,6 +3859,16 @@
           <t>040112</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3595,6 +3955,16 @@
           <t>040112</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3681,6 +4051,16 @@
           <t>040112</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3767,6 +4147,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3853,6 +4243,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3939,6 +4339,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4025,6 +4435,16 @@
           <t>040307</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>UGEL CARAVELI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4109,6 +4529,16 @@
           <t>050621</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4193,6 +4623,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4279,6 +4719,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4365,6 +4815,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4449,6 +4909,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4535,6 +5005,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4621,6 +5101,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4707,6 +5197,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4793,6 +5293,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4879,6 +5389,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4965,6 +5485,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5051,6 +5581,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5137,6 +5677,16 @@
           <t>051005</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5221,6 +5771,16 @@
           <t>050115</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5307,6 +5867,16 @@
           <t>050115</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5393,6 +5963,16 @@
           <t>050115</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5479,6 +6059,16 @@
           <t>050405</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5563,6 +6153,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5649,6 +6249,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5735,6 +6345,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5819,6 +6439,16 @@
           <t>060903</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5905,6 +6535,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5991,6 +6631,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6077,6 +6727,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6161,6 +6821,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6245,6 +6915,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6331,6 +7011,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6415,6 +7105,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6499,6 +7199,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6585,6 +7295,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6669,6 +7389,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6755,6 +7485,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6841,6 +7581,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6927,6 +7677,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7013,6 +7773,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7097,6 +7867,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7183,6 +7963,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7269,6 +8059,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7355,6 +8155,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7441,6 +8251,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7527,6 +8347,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7613,6 +8443,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7699,6 +8539,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7785,6 +8635,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7871,6 +8731,16 @@
           <t>080104</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7957,6 +8827,16 @@
           <t>080104</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8043,6 +8923,16 @@
           <t>080105</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8129,6 +9019,16 @@
           <t>080105</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8215,6 +9115,16 @@
           <t>080105</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8301,6 +9211,16 @@
           <t>080105</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8387,6 +9307,16 @@
           <t>080901</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8473,6 +9403,16 @@
           <t>080901</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8559,6 +9499,16 @@
           <t>080901</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8645,6 +9595,16 @@
           <t>080106</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8731,6 +9691,16 @@
           <t>080106</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8817,6 +9787,16 @@
           <t>080106</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8901,6 +9881,16 @@
           <t>080601</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8985,6 +9975,16 @@
           <t>080601</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9069,6 +10069,16 @@
           <t>080601</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -9155,6 +10165,16 @@
           <t>081201</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9241,6 +10261,16 @@
           <t>081201</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9327,6 +10357,16 @@
           <t>081202</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9413,6 +10453,16 @@
           <t>080108</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9499,6 +10549,16 @@
           <t>080108</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9585,6 +10645,16 @@
           <t>080108</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9669,6 +10739,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9755,6 +10835,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9841,6 +10931,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9927,6 +11027,16 @@
           <t>100603</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10013,6 +11123,16 @@
           <t>100113</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10099,6 +11219,16 @@
           <t>110104</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10185,6 +11315,16 @@
           <t>120107</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10271,6 +11411,16 @@
           <t>120107</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10357,6 +11507,16 @@
           <t>120107</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10443,6 +11603,16 @@
           <t>120114</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10529,6 +11699,16 @@
           <t>120114</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10615,6 +11795,16 @@
           <t>120114</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -10699,6 +11889,16 @@
           <t>120114</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -10785,6 +11985,16 @@
           <t>120114</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -10871,6 +12081,16 @@
           <t>120114</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -10957,6 +12177,16 @@
           <t>120101</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -11043,6 +12273,16 @@
           <t>120101</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11127,6 +12367,16 @@
           <t>120101</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -11213,6 +12463,16 @@
           <t>120101</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11299,6 +12559,16 @@
           <t>120101</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -11385,6 +12655,16 @@
           <t>120101</t>
         </is>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11471,6 +12751,16 @@
           <t>120101</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -11557,6 +12847,16 @@
           <t>120401</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -11643,6 +12943,16 @@
           <t>120401</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -11729,6 +13039,16 @@
           <t>120401</t>
         </is>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -11813,6 +13133,16 @@
           <t>120302</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -11899,6 +13229,16 @@
           <t>120302</t>
         </is>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11985,6 +13325,16 @@
           <t>120302</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -12071,6 +13421,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -12157,6 +13517,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -12243,6 +13613,16 @@
           <t>220805</t>
         </is>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -12329,6 +13709,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>UGEL RIO TAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -12415,6 +13805,16 @@
           <t>120305</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -12501,6 +13901,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -12587,6 +13997,16 @@
           <t>120305</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -12673,6 +14093,16 @@
           <t>120701</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>UGEL TARMA</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -12759,6 +14189,16 @@
           <t>120701</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>UGEL TARMA</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -12845,6 +14285,16 @@
           <t>120701</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>UGEL TARMA</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -12931,6 +14381,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -13017,6 +14477,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -13101,6 +14571,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -13187,6 +14667,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -13273,6 +14763,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -13359,6 +14859,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -13445,6 +14955,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -13531,6 +15051,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -13617,6 +15147,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -13703,6 +15243,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -13789,6 +15339,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -13875,6 +15435,16 @@
           <t>130901</t>
         </is>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -13961,6 +15531,16 @@
           <t>130901</t>
         </is>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -14047,6 +15627,16 @@
           <t>130901</t>
         </is>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14133,6 +15723,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -14219,6 +15819,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -14305,6 +15915,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -14391,6 +16011,16 @@
           <t>130106</t>
         </is>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -14477,6 +16107,16 @@
           <t>130106</t>
         </is>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -14563,6 +16203,16 @@
           <t>130106</t>
         </is>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -14647,6 +16297,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -14731,6 +16391,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -14817,6 +16487,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -14901,6 +16581,16 @@
           <t>150201</t>
         </is>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -14985,6 +16675,16 @@
           <t>150201</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -15071,6 +16771,16 @@
           <t>150201</t>
         </is>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -15157,6 +16867,16 @@
           <t>150801</t>
         </is>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -15243,6 +16963,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -15329,6 +17059,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -15415,6 +17155,16 @@
           <t>150801</t>
         </is>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -15501,6 +17251,16 @@
           <t>150801</t>
         </is>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -15587,6 +17347,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -15673,6 +17443,16 @@
           <t>150801</t>
         </is>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -15759,6 +17539,16 @@
           <t>150801</t>
         </is>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -15845,6 +17635,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -15931,6 +17731,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -16017,6 +17827,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -16103,6 +17923,16 @@
           <t>150120</t>
         </is>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -16189,6 +18019,16 @@
           <t>150120</t>
         </is>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -16275,6 +18115,16 @@
           <t>150120</t>
         </is>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -16361,6 +18211,16 @@
           <t>150510</t>
         </is>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -16447,6 +18307,16 @@
           <t>160201</t>
         </is>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -16533,6 +18403,16 @@
           <t>160201</t>
         </is>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -16619,6 +18499,16 @@
           <t>160201</t>
         </is>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -16703,6 +18593,16 @@
       <c r="R190" t="inlineStr">
         <is>
           <t>160112</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
         </is>
       </c>
     </row>
@@ -16767,6 +18667,8 @@
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -16851,6 +18753,16 @@
           <t>160108</t>
         </is>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -16937,6 +18849,16 @@
           <t>160108</t>
         </is>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -17023,6 +18945,16 @@
           <t>160108</t>
         </is>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -17107,6 +19039,16 @@
           <t>160113</t>
         </is>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -17191,6 +19133,16 @@
           <t>160113</t>
         </is>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -17277,6 +19229,16 @@
           <t>160113</t>
         </is>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -17363,6 +19325,16 @@
           <t>200109</t>
         </is>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -17447,6 +19419,16 @@
       <c r="R199" t="inlineStr">
         <is>
           <t>200104</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
         </is>
       </c>
     </row>
@@ -17515,6 +19497,8 @@
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -17601,6 +19585,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -17687,6 +19681,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -17773,6 +19777,16 @@
           <t>050101</t>
         </is>
       </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -17857,6 +19871,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -17943,6 +19967,16 @@
           <t>200607</t>
         </is>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -18029,6 +20063,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -18115,6 +20159,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -18201,6 +20255,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -18287,6 +20351,16 @@
           <t>220204</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL CÁCERES</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -18373,6 +20447,16 @@
           <t>220901</t>
         </is>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -18459,6 +20543,16 @@
           <t>220901</t>
         </is>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -18545,6 +20639,16 @@
           <t>220909</t>
         </is>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -18631,6 +20735,16 @@
           <t>220901</t>
         </is>
       </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -18717,6 +20831,16 @@
           <t>220910</t>
         </is>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -18803,6 +20927,16 @@
           <t>220901</t>
         </is>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -18889,6 +21023,16 @@
           <t>220809</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -18975,6 +21119,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -19061,6 +21215,16 @@
           <t>220809</t>
         </is>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -19147,6 +21311,16 @@
           <t>230110</t>
         </is>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -19233,6 +21407,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -19319,6 +21503,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -19405,6 +21599,16 @@
           <t>230110</t>
         </is>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -19491,6 +21695,16 @@
           <t>230110</t>
         </is>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -19577,6 +21791,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -19663,6 +21887,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -19749,6 +21983,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -19835,6 +22079,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -19921,6 +22175,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -20007,6 +22271,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -20093,6 +22367,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -20179,6 +22463,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -20265,6 +22559,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -20351,6 +22655,16 @@
           <t>250101</t>
         </is>
       </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -20437,6 +22751,16 @@
           <t>250105</t>
         </is>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -20523,6 +22847,16 @@
           <t>250101</t>
         </is>
       </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -20609,6 +22943,16 @@
           <t>250101</t>
         </is>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -20695,6 +23039,16 @@
           <t>250105</t>
         </is>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -20781,6 +23135,16 @@
           <t>250105</t>
         </is>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -20865,6 +23229,16 @@
           <t>250105</t>
         </is>
       </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -20951,6 +23325,16 @@
           <t>250105</t>
         </is>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -21035,6 +23419,16 @@
       <c r="R241" t="inlineStr">
         <is>
           <t>250105</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T241"/>
+  <dimension ref="A1:U241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -613,6 +618,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -709,6 +719,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -805,6 +820,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -901,6 +921,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -997,6 +1022,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1093,6 +1123,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1187,6 +1222,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1281,6 +1321,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1377,6 +1422,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1473,6 +1523,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1569,6 +1624,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1665,6 +1725,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1759,6 +1824,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1855,6 +1925,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1951,6 +2026,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2047,6 +2127,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2143,6 +2228,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2239,6 +2329,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2335,6 +2430,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2431,6 +2531,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2527,6 +2632,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2623,6 +2733,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2719,6 +2834,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2815,6 +2935,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2911,6 +3036,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3007,6 +3137,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3103,6 +3238,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3199,6 +3339,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3293,6 +3438,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3389,6 +3539,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3485,6 +3640,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3581,6 +3741,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3677,6 +3842,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3773,6 +3943,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3869,6 +4044,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3965,6 +4145,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4061,6 +4246,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4157,6 +4347,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4253,6 +4448,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4349,6 +4549,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4445,6 +4650,11 @@
           <t>UGEL CARAVELI</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4539,6 +4749,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4633,6 +4848,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4729,6 +4949,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4825,6 +5050,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4919,6 +5149,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5015,6 +5250,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5111,6 +5351,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5207,6 +5452,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5303,6 +5553,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5399,6 +5654,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5495,6 +5755,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5591,6 +5856,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5687,6 +5957,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5781,6 +6056,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5877,6 +6157,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5973,6 +6258,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6069,6 +6359,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6163,6 +6458,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6259,6 +6559,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6355,6 +6660,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6449,6 +6759,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6545,6 +6860,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6641,6 +6961,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6737,6 +7062,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6831,6 +7161,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6925,6 +7260,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7021,6 +7361,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7115,6 +7460,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7209,6 +7559,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7305,6 +7660,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7399,6 +7759,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7495,6 +7860,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7591,6 +7961,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7687,6 +8062,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7783,6 +8163,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7877,6 +8262,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7973,6 +8363,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8069,6 +8464,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8165,6 +8565,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8261,6 +8666,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8357,6 +8767,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8453,6 +8868,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8549,6 +8969,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8645,6 +9070,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8741,6 +9171,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8837,6 +9272,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8933,6 +9373,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9029,6 +9474,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9125,6 +9575,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9221,6 +9676,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9317,6 +9777,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9413,6 +9878,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9509,6 +9979,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9605,6 +10080,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9701,6 +10181,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9797,6 +10282,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9891,6 +10381,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9985,6 +10480,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10079,6 +10579,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10175,6 +10680,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10271,6 +10781,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10367,6 +10882,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10463,6 +10983,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10559,6 +11084,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10655,6 +11185,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10749,6 +11284,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10845,6 +11385,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10941,6 +11486,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11037,6 +11587,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11133,6 +11688,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11229,6 +11789,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11325,6 +11890,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11421,6 +11991,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11517,6 +12092,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11613,6 +12193,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -11709,6 +12294,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -11805,6 +12395,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -11899,6 +12494,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -11995,6 +12595,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12091,6 +12696,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12187,6 +12797,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12283,6 +12898,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12377,6 +12997,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12473,6 +13098,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12569,6 +13199,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -12665,6 +13300,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -12761,6 +13401,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -12857,6 +13502,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -12953,6 +13603,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13049,6 +13704,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13143,6 +13803,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13239,6 +13904,11 @@
           <t>UGEL CHANCHAMAYO</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13335,6 +14005,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13431,6 +14106,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13527,6 +14207,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -13623,6 +14308,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -13719,6 +14409,11 @@
           <t>UGEL RIO TAMBO</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -13815,6 +14510,11 @@
           <t>UGEL CHANCHAMAYO</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -13911,6 +14611,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14007,6 +14712,11 @@
           <t>UGEL CHANCHAMAYO</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14103,6 +14813,11 @@
           <t>UGEL TARMA</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14199,6 +14914,11 @@
           <t>UGEL TARMA</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14295,6 +15015,11 @@
           <t>UGEL TARMA</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14391,6 +15116,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14487,6 +15217,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14581,6 +15316,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -14677,6 +15417,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -14773,6 +15518,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -14869,6 +15619,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -14965,6 +15720,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15061,6 +15821,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15157,6 +15922,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15253,6 +16023,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15349,6 +16124,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15445,6 +16225,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -15541,6 +16326,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -15637,6 +16427,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -15733,6 +16528,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -15829,6 +16629,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -15925,6 +16730,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16021,6 +16831,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16117,6 +16932,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16213,6 +17033,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16307,6 +17132,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16401,6 +17231,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16497,6 +17332,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -16591,6 +17431,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -16685,6 +17530,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -16781,6 +17631,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -16877,6 +17732,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -16973,6 +17833,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17069,6 +17934,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17165,6 +18035,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17261,6 +18136,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17357,6 +18237,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -17453,6 +18338,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -17549,6 +18439,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -17645,6 +18540,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -17741,6 +18641,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -17837,6 +18742,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -17933,6 +18843,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18029,6 +18944,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18125,6 +19045,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18221,6 +19146,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18317,6 +19247,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -18413,6 +19348,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -18509,6 +19449,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -18605,6 +19550,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -18661,14 +19611,47 @@
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>367188</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>MAYNAS</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>BELEN</t>
+        </is>
+      </c>
       <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>160112</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -18763,6 +19746,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -18859,6 +19847,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -18955,6 +19948,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19049,6 +20047,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19143,6 +20146,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19239,6 +20247,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -19335,6 +20348,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -19431,6 +20449,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -19492,13 +20515,42 @@
           <t>081811</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>SAN RAMON</t>
+        </is>
+      </c>
       <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>120305</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -19595,6 +20647,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -19691,6 +20748,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -19787,6 +20849,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -19881,6 +20948,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -19977,6 +21049,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20073,6 +21150,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -20169,6 +21251,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -20265,6 +21352,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -20361,6 +21453,11 @@
           <t>UGEL MARISCAL CÁCERES</t>
         </is>
       </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -20457,6 +21554,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -20553,6 +21655,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -20649,6 +21756,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -20745,6 +21857,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -20841,6 +21958,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -20937,6 +22059,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21033,6 +22160,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -21129,6 +22261,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -21225,6 +22362,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -21321,6 +22463,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -21417,6 +22564,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -21513,6 +22665,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -21609,6 +22766,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -21705,6 +22867,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -21801,6 +22968,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -21897,6 +23069,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -21993,6 +23170,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -22089,6 +23271,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -22185,6 +23372,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -22281,6 +23473,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -22377,6 +23574,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -22473,6 +23675,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -22569,6 +23776,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -22665,6 +23877,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -22761,6 +23978,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -22857,6 +24079,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -22953,6 +24180,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -23049,6 +24281,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -23145,6 +24382,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -23239,6 +24481,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -23335,6 +24582,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -23429,6 +24681,11 @@
       <c r="T241" t="inlineStr">
         <is>
           <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>FONCODES</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U241"/>
+  <dimension ref="A1:W241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -620,6 +630,16 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>54005 MIGUEL GRAU/MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -721,6 +741,16 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -822,6 +852,16 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -923,6 +963,16 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>54006 SAGRADO CORAZON DE JESUS/54006 SAGRADO CORAZON DE JESUS/54006 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1024,6 +1074,16 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>661/FRANCISCO BOLOGNESI/55001 MANUEL JESUS SIERRA A.</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1125,6 +1185,16 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>AURORA INES TEJADA/AURORA INES TEJADA/AURORA INES TEJADA/AURORA INES TEJADA</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1224,6 +1294,16 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>DIVINO MAESTRO/55005</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1323,6 +1403,16 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>54930/55006/55006/55006</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1424,6 +1514,16 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>54490 HOGAR DE CRISTO</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1525,6 +1625,16 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>54104 CRISTO REY/54104</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1626,6 +1736,16 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>54105 JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1727,6 +1847,16 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>55006-20 ESCUELA CONCERTADA SOLARIS/55006-20 ESCUELA CONCERTADA SOLARIS/55006-20 ESCUELA CONCERTADA SOLARIS</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1826,6 +1956,16 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>278/54178</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -1927,6 +2067,16 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
+          <t>277-21 EL BUEN PASTOR/54177 EL BUEN PASTOR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2028,6 +2178,16 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
+          <t>40034 MARIO VARGAS LLOSA/40034 MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2129,6 +2289,16 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>40222 DIEGO THOMSON/40222 DIEGO THOMSON/40222 DIEGO THOMSON</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2230,6 +2400,16 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>SAN MARTIN DE PORRES/SAN MARTIN DE PORRES/SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2331,6 +2511,16 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>40227 EDUARDO PORTUGAL/40227 EDUARDO PORTUGAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2432,6 +2622,16 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>41040 JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2533,6 +2733,16 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>41041 CRISTO REY/41041 CRISTO REY/41041 CRISTO REY</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2634,6 +2844,16 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
+          <t>40616 CASIMIRO CUADROS I/40616 CASIMIRO CUADROS I/40616 CASIMIRO CUADROS I</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2735,6 +2955,16 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>LEON XIII/LEON XIII/LEON XIII</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2836,6 +3066,16 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>40044 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -2937,6 +3177,16 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
+          <t>SAN JOSE DE COTTOLENGO/SAN JOSE DE COTTOLENGO/SAN JOSE DE COTTOLENGO</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3038,6 +3288,16 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
+          <t>SAN PIO X/SAN PIO X/SAN PIO X</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3139,6 +3399,16 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
+          <t>40035 V. A. BELAUNDE/40035 V. A. BELAUNDE</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3240,6 +3510,16 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI/40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI/40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI/40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3341,6 +3621,16 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>41026 MARIA MURILLO DE BERNAL/41026 MARIA MURILLO DE BERNAL</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3440,6 +3730,16 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>40206/40206</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3541,6 +3841,16 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>40207 MARIANO MELGAR VALDIVIESO</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3642,6 +3952,16 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
+          <t>SAN ANTONIO MARIA CLARET/SAN ANTONIO MARIA CLARET/SAN ANTONIO MARIA CLARET</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3743,6 +4063,16 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
+          <t>40230 SAN ANTONIO DEL PEDREGAL/40230 SAN ANTONIO DEL PEDREGAL/40230 SAN ANTONIO DEL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3844,6 +4174,16 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>ALMIRANTE MIGUEL GRAU/ALMIRANTE MIGUEL GRAU/ALMIRANTE MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -3945,6 +4285,16 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
+          <t>CORONEL FRANCISCO BOLOGNESI/CORONEL FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4046,6 +4396,16 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>NEPTALI VALDERRAMA AMPUERO/NEPTALI VALDERRAMA AMPUERO/NEPTALI VALDERRAMA AMPUERO</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4147,6 +4507,16 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>PADRE PEREZ DE GUEREÑU/PADRE PEREZ DE GUEREÑU/PADRE PEREZ DE GUEREÑU</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4248,6 +4618,16 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
+          <t>SOR ANA/SOR ANA/SOR ANA</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4349,6 +4729,16 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
+          <t>40202 CHARLOTTE/40202 CHARLOTTE/40202 CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4450,6 +4840,16 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA/40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA/40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4551,6 +4951,16 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>JORGE SANJINEZ LENZ/JORGE SANJINEZ LENZ/JORGE SANJINEZ LENZ</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4652,6 +5062,16 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>40272 JOSE OLAYA BALANDRA</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4751,6 +5171,16 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>24397</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4850,6 +5280,16 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>38083</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -4951,6 +5391,16 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>38984-12 CARLOS LABORDE/38984-12 CARLOS LABORDE</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5052,6 +5502,16 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
+          <t>39009 EL MAESTRO/39009 EL MAESTRO</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5151,6 +5611,16 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>38018 DE MARAVILLAS/38018</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5252,6 +5722,16 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>39003 CORAZON DE JESUS/39003 CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5353,6 +5833,16 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>38001 GUSTAVO CASTRO PANTOJA/38001 GUSTAVO CASTRO PANTOJA</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5454,6 +5944,16 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>MARIA PARADO DE BELIDO/39002 MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5555,6 +6055,16 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>CIRO ALEGRIA/LUIS CARRANZA/CIRO ALEGRIA/LUIS CARRANZA</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5656,6 +6166,16 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>MELITON CARVAJAL/MELITON CARVAJAL</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5757,6 +6277,16 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE FATIMA/NUESTRA SEÑORA DE FATIMA/NUESTRA SEÑORA DE FATIMA/331JARDIN DE NIÑOS/NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5858,6 +6388,16 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
+          <t>SAN RAMON/SAN RAMON/SAN RAMON</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -5959,6 +6499,16 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
+          <t>SAN AGUSTIN</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6058,6 +6608,16 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>38020</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6159,6 +6719,16 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
+          <t>104 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6260,6 +6830,16 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
+          <t>38019 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6361,6 +6941,16 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
+          <t>38276 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6460,6 +7050,16 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
+          <t>38867</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6561,6 +7161,16 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
+          <t>38984-3 JOSE ABELARDO QUIÑONES/JOSE ABELARDO QUIÑONES GONZALES/38984-3 JOSE ABELARDO QUIÑONES</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6662,6 +7272,16 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 50 PADRE CARLOS SCHMIDT SJ/FE Y ALEGRIA 50 PADRE CARLOS SCHMIDT SJ/FE Y ALEGRIA 50 PADRE CARLOS SCHMIDT SJ</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6761,6 +7381,16 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
+          <t>16499/16499</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6862,6 +7492,16 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
+          <t>82001 SAN RAMON</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -6963,6 +7603,16 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>82002 TARCISIO ZEGARRA</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7064,6 +7714,16 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>821228 EL INGENIO</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7163,6 +7823,16 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
+          <t>82005</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7262,6 +7932,16 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
+          <t>82028/82028</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7363,6 +8043,16 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
+          <t>82008/82008 SANTA BEATRIZ DE SILVA</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7462,6 +8152,16 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
+          <t>82031</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7561,6 +8261,16 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
+          <t>83004</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7662,6 +8372,16 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LA MERCED/82003 NUESTRA SEÑORA DE LA MERCED/NUESTRA SEÑORA DE LA MERCED/NUESTRA SEÑORA DE LA MERCED</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7761,6 +8481,16 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7862,6 +8592,16 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
+          <t>82015 RAFAEL OLASCOAGA/82015 RAFAEL OLASCOAGA</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -7963,6 +8703,16 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
+          <t>JORGE CHAVEZ CHAPARRO/50022 JORGE CHAVEZ CHAPARRO</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8064,6 +8814,16 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
+          <t>50023 REPUBLICA DE MEXICO</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8165,6 +8925,16 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
+          <t>INCA GARCILASO DE LA VEGA/INCA GARCILASO DE LA VEGA/INCA GARCILASO DE LA VEGA/INCA GARCILASO DE LA VEGA</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8264,6 +9034,16 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8365,6 +9145,16 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
+          <t>50707 SIMON BOLIVAR/50707 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8466,6 +9256,16 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
+          <t>CLORINDA MATTO DE TURNER/CLORINDA MATTO DE TURNER/CLORINDA MATTO DE TURNER/CLORINDA MATTO DE TURNER/CLORINDA MATTO DE TURNER</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8567,6 +9367,16 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
+          <t>50900 EDUCANDAS/50900 EDUCANDAS</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8668,6 +9478,16 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
+          <t>51015 SAN FRANCISCO DE BORJA/51015 SAN FRANCISCO DE BORJA/51015 SAN FRANCISCO DE BORJA</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8769,6 +9589,16 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
+          <t>GLORIOSO COLEGIO NACIONAL DE CIENCIAS/GLORIOSO COLEGIO NACIONAL DE CIENCIAS/GLORIOSO COLEGIO NACIONAL DE CIENCIAS/GLORIOSO COLEGIO NACIONAL DE CIENCIAS</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8870,6 +9700,16 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
+          <t>56175 SAGRADO CORAZON DE JESUS/56175 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -8971,6 +9811,16 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
+          <t>56207 RICARDO PALMA SORIANO/56207 RICARDO PALMA SORIANO</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9072,6 +9922,16 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
+          <t>CORONEL LADISLAO ESPINAR/CORONEL LADISLAO ESPINAR/CORONEL LADISLAO ESPINAR/CORONEL LADISLAO ESPINAR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9173,6 +10033,16 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
+          <t>50038 ALEJANDRO VELASCO ASTETE/50038 ALEJANDRO VELASCO ASTETE/50038 ALEJANDRO VELASCO ASTETE/50038 ALEJANDRO VELASCO ASTETE/50038 ALEJANDRO VELASCO ASTETE</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9274,6 +10144,16 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
+          <t>51023 SAN LUIS GONZAGA/51023 SAN LUIS GONZAGA/51023 SAN LUIS GONZAGA</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9375,6 +10255,16 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
+          <t>BOLIVARIANO/BOLIVARIANO/BOLIVARIANO</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9476,6 +10366,16 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
+          <t>DIEGO QUISPE TITO/DIEGO QUISPE TITO/DIEGO QUISPE TITO/DIEGO QUISPE TITO/DIEGO QUISPE TITO</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9577,6 +10477,16 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
+          <t>REVOLUCIONARIA SANTA ROSA/REVOLUCIONARIA SANTA ROSA/REVOLUCIONARIA SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9678,6 +10588,16 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
+          <t>VIRGEN DE FATIMA/VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9779,6 +10699,16 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
+          <t>50226 LA INMACULADA/50226 LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9880,6 +10810,16 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
+          <t>51027 JUAN DE LA CRUZ MONTES SALAS/51027 JUAN DE LA CRUZ MONTES SALAS/51027 JUAN DE LA CRUZ MONTES SALAS</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -9981,6 +10921,16 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
+          <t>51028 EL ROSARIO</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10082,6 +11032,16 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
+          <t>51006 TUPAC AMARU/51006 TUPAC AMARU/51006 TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10183,6 +11143,16 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 20/FE Y ALEGRIA 20</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10284,6 +11254,16 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
+          <t>GRAN MARISCAL ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10383,6 +11363,16 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
+          <t>MATEO PUMACAHUA/MATEO PUMACAHUA/MATEO PUMACAHUA/56001</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10482,6 +11472,16 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
+          <t>56004/JAPAM/56004</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10581,6 +11581,16 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
+          <t>57001 JORGE CHAVEZ/57001</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10682,6 +11692,16 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
+          <t>51030 LUIS NAVARRETE/51030 LUIS NAVARRETE/51030 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10783,6 +11803,16 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
+          <t>MARIANO SANTOS</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10884,6 +11914,16 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
+          <t>SAN IGNACIO DE LOYOLA FE Y ALEGRIA 44/SAN IGNACIO DE LOYOLA FE Y ALEGRIA 44</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -10985,6 +12025,16 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
+          <t>50025 DANIEL ESTRADA PEREZ/50025 DANIEL ESTRADA PEREZ</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11086,6 +12136,16 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
+          <t>50032 MIGUEL GRAU SEMINARIO/50032 MIGUEL GRAU SEMINARIO</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11187,6 +12247,16 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
+          <t>URIEL GARCIA/URIEL GARCIA/URIEL GARCIA/URIEL GARCIA</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11286,6 +12356,16 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
+          <t>56435/56435</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11387,6 +12467,16 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
+          <t>56176 GENERAL JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11488,6 +12578,16 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
+          <t>57003 ALMIRANTE MIGUEL GRAU/57003 ALMIRANTE MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11589,6 +12689,16 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
+          <t>SAN ISIDRO/SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11690,6 +12800,16 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
+          <t>845/HORACIO ZEBALLOS GAMES/HORACIO ZEBALLOS GAMES</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11791,6 +12911,16 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
+          <t>22526 MEDARDO JESUS APARCANA HERNANDEZ/22526 MEDARDO JESUS APARCANA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11892,6 +13022,16 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
+          <t>30012 VICTOR ALBERTO GIL MALLMA/30012 VICTOR ALBERTO GIL MALLMA</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -11993,6 +13133,16 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
+          <t>30153 MARIA N. SALAZAR AGUILAR/30153 MARIA N. SALAZAR AGUILAR</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12094,6 +13244,16 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
+          <t>30155 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12195,6 +13355,16 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
+          <t>30216 SAGRADO CORAZON DE MARIA</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12296,6 +13466,16 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
+          <t>31509/31509 RICARDO MENENDEZ MENENDEZ/RICARDO MENENDEZ MENENDEZ</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12397,6 +13577,16 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
+          <t>31593 JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12496,6 +13686,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
+          <t>30209/30209</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12597,6 +13797,16 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
+          <t>30225 LA ALBORADA</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12698,6 +13908,16 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
+          <t>31595/31595 FLORENCIO V. HINOSTROZA C.</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12799,6 +14019,16 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
+          <t>30059 ROSA DE AMERICA</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12900,6 +14130,16 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
+          <t>31507 DOMINGO F. SARMIENTO</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -12999,6 +14239,16 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13100,6 +14350,16 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
+          <t>31542 VIRGEN MARIA ADMIRABLE</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13201,6 +14461,16 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
+          <t>31554 JOSE C. MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13302,6 +14572,16 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
+          <t>31541 EMMA LUZMILA CALLE VERGARA</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13403,6 +14683,16 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
+          <t>406 LA ASUNCION/31363 LA ASUNCION/LA ASUNCION</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13504,6 +14794,16 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
+          <t>SAN JOSE/SAN JOSE/SAN JOSE</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13605,6 +14905,16 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
+          <t>SAN VICENTE DE PAUL/SAN VICENTE DE PAUL/SAN VICENTE DE PAUL</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13706,6 +15016,16 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
+          <t>SAN VICENTE DE PAUL/SAN VICENTE DE PAUL/SAN VICENTE DE PAUL</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13805,6 +15125,16 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
+          <t>31886/31886</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -13906,6 +15236,16 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
+          <t>PERENE/PERENE/PERENE/PERENE</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14007,6 +15347,16 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
+          <t>RICARDO PALMA SORIANO/RICARDO PALMA SORIANO/RICARDO PALMA SORIANO</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14108,6 +15458,16 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI/JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14209,6 +15569,16 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
+          <t>LOS ANGELES/LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14310,6 +15680,16 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14411,6 +15791,16 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
+          <t>DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14512,6 +15902,16 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
+          <t>30765 JUAN SANTOS ATAHUALPA/30765 JUAN SANTOS ATAHUALPA/30765 JUAN SANTOS ATAHUALPA</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14613,6 +16013,16 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14714,6 +16124,16 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
+          <t>SAN RAMON/SAN RAMON/SAN RAMON/SAN RAMON</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14815,6 +16235,16 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
+          <t>31517 ANGELA MORENO DE GALVEZ/31517 ANGELA MORENO DE GALVEZ</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -14916,6 +16346,16 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
+          <t>31518 JOSE GALVEZ BARRENECHEA/31518 JOSE GALVEZ BARRENECHEA</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15017,6 +16457,16 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
+          <t>SANTA TERESA</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15118,6 +16568,16 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
+          <t>80092 CARLOS WIESSE/80092 CARLOS WIESSE/80092 CARLOS WIESSE/80092 CARLOS WIESSE/80092 CARLOS WIESSE</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15219,6 +16679,16 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
+          <t>81770 MARIA INMACULADA CONCEPCION/81770 MARIA INMACULADA CONCEPCION/81770 MARIA INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15318,6 +16788,16 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15419,6 +16899,16 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
+          <t>82070 ABRAHAM VALDELOMAR/82070 ABRAHAM VALDELOMAR</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15520,6 +17010,16 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
+          <t>82206 VALLE DE DIOS/82206 VALLE DE DIOS</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15621,6 +17121,16 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
+          <t>1579 CORAZON DEL NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15722,6 +17232,16 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
+          <t>80823 EL INDOAMERICANO/80823 EL INDOAMERICANO</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15823,6 +17343,16 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
+          <t>82049 RAMON CASTILLA MARQUESADO/82049 RAMON CASTILLA MARQUESADO</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -15924,6 +17454,16 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
+          <t>1566 EL PILOTO</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16025,6 +17565,16 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
+          <t>80756 JOSE MARIA ARGUEDAS/80756 JOSE MARIA ARGUEDAS/80756 JOSE MARIA ARGUEDAS</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16126,6 +17676,16 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
+          <t>80819 FRANCISCO LIZARZABURO/80819 FRANCISCO LIZARZABURO/80819 FRANCISCO LIZARZABURO/80819 FRANCISCO LIZARZABURO</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16227,6 +17787,16 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
+          <t>80127 MAYOR SANTIAGO ZAVALA/80127 MAYOR SANTIAGO ZAVALA</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16328,6 +17898,16 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
+          <t>80132 NESTOR GASTAÑADUI SANCHEZ/80132 NESTOR GASTAÑADUI SANCHEZ</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16429,6 +18009,16 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
+          <t>80779 LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16530,6 +18120,16 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
+          <t>1576 JERUSALEN</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16631,6 +18231,16 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
+          <t>80038 SAN FRANCISCO DE ASIS/80038 SAN FRANCISCO DE ASIS/80038 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16732,6 +18342,16 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
+          <t>81749 DIVINO JESUS/81749 DIVINO JESUS</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16833,6 +18453,16 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
+          <t>80044 SAN MARTIN DE PORRES/80044 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -16934,6 +18564,16 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
+          <t>81583 LA MERCED/81583 LA MERCED</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17035,6 +18675,16 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
+          <t>ANTENOR ORREGO ESPINOZA/ANTENOR ORREGO ESPINOZA</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17134,6 +18784,16 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
+          <t>80091/80091/80091</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17233,6 +18893,16 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
+          <t>81700/81700</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17334,6 +19004,16 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
+          <t>VIRU/VIRU/VIRU</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17433,6 +19113,16 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
+          <t>20478</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17532,6 +19222,16 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
+          <t>21012</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17633,6 +19333,16 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
+          <t>21011 VIRGEN DE LOURDES/21011 VIRGEN DE LOURDES</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17734,6 +19444,16 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
+          <t>20325 SAN JOSE DE MANZANARES/20325 SAN JOSE DE MANZANARES/20325 SAN JOSE DE MANZANARES</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17835,6 +19555,16 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
+          <t>20390 HORTENCIA DULANTO DE LAS CASAS/20390 HORTENCIA DULANTO DE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -17936,6 +19666,16 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
+          <t>20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18037,6 +19777,16 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
+          <t>658/20318 JOSE ANTONIO MACNAMARA</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18138,6 +19888,16 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
+          <t>20321 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18239,6 +19999,16 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
+          <t>20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18340,6 +20110,16 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
+          <t>20827 MERCEDES INDACOCHEA LOZANO/20827 MERCEDES INDACOCHEA LOZANO</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18441,6 +20221,16 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
+          <t>20827 MERCEDES INDACOCHEA LOZANO/20827 MERCEDES INDACOCHEA LOZANO</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18542,6 +20332,16 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
+          <t>20391 JORGE BRAVO DE RUEDA QUEROL/20391 JORGE BRAVO DE RUEDA QUEROL</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18643,6 +20443,16 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
+          <t>21010 CLARA NICHOS MANSILLA/21010 CLARA NICHOS MANSILLA</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18744,6 +20554,16 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
+          <t>87 EMILIA BARCIA BONIFFATTI</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18845,6 +20665,16 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
+          <t>106 JUAN RAGGIO CHICHIZOLA</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -18946,6 +20776,16 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
+          <t>1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19047,6 +20887,16 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
+          <t>1104 CRNEL. FAP VICTOR MALDONADO BEGAZO</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19148,6 +20998,16 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
+          <t>20167 MANUEL GONZALES PRADA/20167 MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19249,6 +21109,16 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
+          <t>62006 JOSE DAMASO RAMOS BOSMEDIANO</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19350,6 +21220,16 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
+          <t>62007 JOSE MARIA ARGUEDAS/62007 JOSE MARIA ARGUEDAS</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19451,6 +21331,16 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
+          <t>62010 VIRGEN DE FATIMA/62010 VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19552,6 +21442,16 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
+          <t>61006 SARA ALICIA SABERBEIN PINEDO</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19649,6 +21549,16 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
+          <t>SAGRADA FAMILIA</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19748,6 +21658,16 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
+          <t>6010120/6010120</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19849,6 +21769,16 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
+          <t>165 REPUBLICA FEDERAL DE ALEMANIA</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -19950,6 +21880,16 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
+          <t>61015 LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20049,6 +21989,16 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20148,6 +22098,16 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
+          <t>601515/601515</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20249,6 +22209,16 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
+          <t>318 GLORIA CHAVEZ CULQUI</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20350,6 +22320,16 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
+          <t>14122 VIRGEN DEL TRANSITO</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20451,6 +22431,16 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
+          <t>MARIA GORETTI/MARIA GORETTI</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20548,6 +22538,16 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
+          <t>ANEXO-SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20649,6 +22649,16 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
+          <t>14620 SEÑOR DE LA DIVINA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20750,6 +22760,16 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
+          <t>JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20851,6 +22871,16 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
+          <t>SAN RAMON/SAN RAMON/SAN RAMON/SAN RAMON</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -20950,6 +22980,16 @@
       </c>
       <c r="U204" t="inlineStr">
         <is>
+          <t>15030 DIVINO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21051,6 +23091,16 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
+          <t>14860 DIVINO CORAZON DE JESUS/14860 DIVINO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21152,6 +23202,16 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
+          <t>14011 NUESTRA SEÑORA DEL PILAR/14011 NUESTRA SEÑORA DEL PILAR/14011 NUESTRA SEÑORA DEL PILAR</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21253,6 +23313,16 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
+          <t>LUIS ALBERTO SANCHEZ SANCHEZ/LUIS ALBERTO SANCHEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21354,6 +23424,16 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
+          <t>SEÑOR DE LA DIVINA MISERICORDIA/SEÑOR DE LA DIVINA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21455,6 +23535,16 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
+          <t>0243 JOSE ALEXANDER RENGIFO GONZALES/0243 JOSE ALEXANDER RENGIFO GONZALES</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21556,6 +23646,16 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
+          <t>0750 ELSA PEREA FLORES/0750 ELSA PEREA FLORES/0750 ELSA PEREA FLORES</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21657,6 +23757,16 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
+          <t>MIGUEL CHUQUISENGO RAMIREZ/MIGUEL CHUQUISENGO RAMIREZ</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21758,6 +23868,16 @@
       </c>
       <c r="U212" t="inlineStr">
         <is>
+          <t>VIRGEN DOLOROSA/VIRGEN DOLOROSA</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21859,6 +23979,16 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
+          <t>326 MI DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -21960,6 +24090,16 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
+          <t>FRANCISCO IZQUIERDO RIOS/FRANCISCO IZQUIERDO RIOS/FRANCISCO IZQUIERDO RIOS/FRANCISCO IZQUIERDO RIOS/FRANCISCO IZQUIERDO RIOS</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22061,6 +24201,16 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
+          <t>TARAPOTO/TARAPOTO/TARAPOTO</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22162,6 +24312,16 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
+          <t>00543 TEOBALDO SEGUNDO LOPEZ CHUMBE</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22263,6 +24423,16 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALES PRADA/MANUEL GONZALES PRADA/MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22364,6 +24534,16 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
+          <t>MARCELINO CHAVEZ VILLAVERDE</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22465,6 +24645,16 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
+          <t>42253 GERARDO ARIAS COPAJA/42253 GERARDO ARIAS COPAJA</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22566,6 +24756,16 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
+          <t>43006 MERCEDES INDACOCHEA/43006 MERCEDES INDACOCHEA</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22667,6 +24867,16 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
+          <t>42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22768,6 +24978,16 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
+          <t>42237 JORGE CHAVEZ/MARIA ROSARIO ARAOZ/MARIA ROSARIO ARAOZ/42237 JORGE CHAVEZ/42237 JORGE CHAVEZ</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22869,6 +25089,16 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
+          <t>42257 NUESTRO SEÑOR DE LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -22970,6 +25200,16 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
+          <t>43009 MARIA UGARTECHE DE MACLEAN/43009 MARIA UGARTECHE DE MACLEAN</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23071,6 +25311,16 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
+          <t>CORONEL BOLOGNESI/CORONEL BOLOGNESI/CORONEL BOLOGNESI/CORONEL BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23172,6 +25422,16 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
+          <t>SAN JOSE FE Y ALEGRIA 40/SAN JOSE FE Y ALEGRIA 40</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23273,6 +25533,16 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
+          <t>43001 HERMANOS BARRETO</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23374,6 +25644,16 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
+          <t>CARLOS ARMANDO LAURA/CARLOS ARMANDO LAURA/43003 CARLOS ARMANDO LAURA/43003 CARLOS ARMANDO LAURA</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23475,6 +25755,16 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
+          <t>SAN MARTIN DE PORRES/SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23576,6 +25866,16 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
+          <t>42005 JOSE ROSA ARA/42005 JOSE ROSA ARA</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23677,6 +25977,16 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
+          <t>42010 SANTISIMA NIÑA MARIA/42010 SANTISIMA NIÑA MARIA</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23778,6 +26088,16 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
+          <t>42019 LASTENIA REJAS DE CASTAÑON/42019 LASTENIA REJAS DE CASTAÑON/42019 LASTENIA REJAS DE CASTAÑON</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23879,6 +26199,16 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
+          <t>JORGE ALBERTO RENGIFO PRADA/JORGE ALBERTO RENGIFO PRADA/64359 JOSE GALVEZ EGUSQUIZA/64359 JOSE GALVEZ EGUSQUIZA</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -23980,6 +26310,16 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
+          <t>64567 MIRAFLORES/64567 MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -24081,6 +26421,16 @@
       </c>
       <c r="U235" t="inlineStr">
         <is>
+          <t>64753 FAUSTINO MALDONADO/64753 FAUSTINO MALDONADO/64753 FAUSTINO MALDONADO/64753 FAUSTINO MALDONADO</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -24182,6 +26532,16 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
+          <t>290 LA CASITA DEL SABER</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -24283,6 +26643,16 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
+          <t>64789 JOSE FAUSTINO SANCHEZ CARRION/64789 JOSE FAUSTINO SANCHEZ CARRION/64789 JOSE FAUSTINO SANCHEZ CARRION</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -24384,6 +26754,16 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
+          <t>ALFREDO VARGAS GUERRA/ALFREDO VARGAS GUERRA/64865 ALFREDO VARGAS GUERRA/ALFREDO VARGAS GUERRA</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -24483,6 +26863,16 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
+          <t>LA PERLA/64668</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -24584,6 +26974,16 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
+          <t>64093 EDITA BRITO MAINAS/64093 EDITA BRITO MAINAS</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
           <t>FONCODES</t>
         </is>
       </c>
@@ -24684,6 +27084,16 @@
         </is>
       </c>
       <c r="U241" t="inlineStr">
+        <is>
+          <t>64103 TENIENTE DIEGO FERRE/64103 TENIENTE DIEGO FERRE/64103 TENIENTE DIEGO FERRE</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
         <is>
           <t>FONCODES</t>
         </is>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_foncode_2026.xlsx
@@ -419,62 +419,62 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>COD. MODULAR</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PROVINCIA</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>DISTRITO</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>NOMBRE IE</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>TIPO DE MANTENIMIENTO</t>
+          <t>tipo_de_mantenimiento</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>MONTO DE LA INTERVENCIÓN 2026</t>
+          <t>monto_de_la_intervencion_2026</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>% AVANCE</t>
+          <t>avance</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ESTADO PROYECTO</t>
+          <t>estado_proyecto</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>FECHA DE INICIO</t>
+          <t>fecha_de_inicio</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>FECHA DE CULMINACION ESTIMADA</t>
+          <t>fecha_de_culminacion_estimada</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -484,17 +484,17 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>departamento_2</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>provincia_2</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>distrito_2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>829330</t>
+          <t>094659</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>821228 EL INGENIO</t>
+          <t>098</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>081811</t>
+          <t>234891</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -22520,7 +22520,11 @@
           <t>SAN RAMON</t>
         </is>
       </c>
-      <c r="Q200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>SAN RAMON</t>
+        </is>
+      </c>
       <c r="R200" t="inlineStr">
         <is>
           <t>120305</t>
@@ -22538,7 +22542,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>ANEXO-SAGRADO CORAZON DE JESUS</t>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
